--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-schedule-type.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-schedule-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -498,7 +498,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -510,7 +512,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-schedule-type.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-schedule-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -498,9 +498,7 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>44</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -512,9 +510,7 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>46</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-schedule-type.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-schedule-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -498,7 +498,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -510,7 +512,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
